--- a/output/pdf_financials_xlsx/LMN.xlsx
+++ b/output/pdf_financials_xlsx/LMN.xlsx
@@ -1061,16 +1061,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>67.08499999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>146.509</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>210.983</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>352.441</v>
       </c>
     </row>
     <row r="35">
@@ -1099,16 +1099,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>67.08499999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>146.509</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>210.983</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>352.441</v>
       </c>
     </row>
     <row r="37">
@@ -1327,16 +1327,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>99.977</v>
+        <v>32.892</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>231.229</v>
+        <v>84.72</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>294.148</v>
+        <v>83.16500000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>451.796</v>
+        <v>99.355</v>
       </c>
     </row>
     <row r="49">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/LMN.xlsx
+++ b/output/pdf_financials_xlsx/LMN.xlsx
@@ -959,16 +959,16 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>37.139</v>
+        <v>31.836</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>88.212</v>
+        <v>80.322</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>117.303</v>
+        <v>108.058</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>116.468</v>
+        <v>108.369</v>
       </c>
     </row>
     <row r="29">
@@ -978,16 +978,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>73.017</v>
+        <v>67.714</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2729.493</v>
+        <v>-2737.383</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-121.916</v>
+        <v>-131.161</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>267.054</v>
+        <v>258.955</v>
       </c>
     </row>
     <row r="30">
@@ -997,16 +997,16 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>28.55070480361298</v>
+        <v>26.47715497859195</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-546.2602242684658</v>
+        <v>-547.8392695964728</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-18.24079476936427</v>
+        <v>-19.62401065278214</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>34.87892798370034</v>
+        <v>33.82114776793877</v>
       </c>
     </row>
     <row r="31">
@@ -2321,16 +2321,16 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>31.836</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>80.322</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>108.058</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>108.369</v>
       </c>
     </row>
     <row r="101">
@@ -2558,7 +2558,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.169</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5770,7 +5770,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
@@ -6130,7 +6134,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -7538,7 +7542,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">

--- a/output/pdf_financials_xlsx/LMN.xlsx
+++ b/output/pdf_financials_xlsx/LMN.xlsx
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>2.069</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>6.358</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>4.249</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>3.149</v>
       </c>
     </row>
     <row r="71">
@@ -1772,16 +1772,16 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>2.069</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>6.358</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>4.249</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>3.149</v>
       </c>
     </row>
     <row r="72">
@@ -1848,16 +1848,16 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>48.187</v>
+        <v>46.118</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>4494.26</v>
+        <v>4487.902</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>20.862</v>
+        <v>16.613</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>21.649</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="76">
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0</v>
+        <v>4.719</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
+        <v>6.921</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0</v>
+        <v>3.621</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>3.631</v>
       </c>
     </row>
     <row r="79">
@@ -1924,16 +1924,16 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0</v>
+        <v>4.719</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0</v>
+        <v>6.921</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>3.621</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0</v>
+        <v>3.631</v>
       </c>
     </row>
     <row r="80">
@@ -1942,25 +1942,17 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.04414098062166732</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>-0.003455881491814436</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.01159532179596359</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.008276953202253089</v>
       </c>
     </row>
     <row r="81">
@@ -2046,16 +2038,16 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>63.95</v>
+        <v>59.231</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>294.812</v>
+        <v>287.891</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>391.299</v>
+        <v>387.678</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>327.868</v>
+        <v>324.237</v>
       </c>
     </row>
     <row r="86">
@@ -2568,16 +2560,16 @@
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>0</v>
+        <v>-113.186</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>0</v>
+        <v>-352.349</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0</v>
+        <v>-145.271</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0</v>
+        <v>-20.461</v>
       </c>
     </row>
     <row r="114">
@@ -3470,7 +3462,11 @@
           <t>Intangible assets and goodwill (note 8)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GoodwillAndOtherIntangibleAssets</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>208.053</v>
       </c>
@@ -3782,7 +3778,11 @@
           <t>Lease obligations (note 11)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -3956,7 +3956,11 @@
           <t>Lease obligations (note 11)</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -4582,7 +4586,11 @@
           <t>Lease obligations (note 12)</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>2.069</v>
       </c>
@@ -4714,7 +4722,11 @@
           <t>Lease obligations (note 12)</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
         <v>4.719</v>
       </c>
@@ -5000,7 +5012,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -5632,7 +5648,11 @@
           <t>Acquisition of businesses (note 4)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -6064,7 +6084,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E87" s="5" t="n">
         <v>27.402</v>
       </c>
@@ -6726,7 +6750,11 @@
           <t>Acquisition of businesses (note 4)</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E107" s="5" t="n">
         <v>-113.186</v>
       </c>
